--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260622.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>250,907,097</t>
+          <t>14,326,665</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>14,326,665</t>
+          <t>250,907,097</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>334,291,396</t>
+          <t>7,296,513</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>7,296,513</t>
+          <t>334,291,396</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>237,744,653</t>
+          <t>104,888,476</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>104,888,476</t>
+          <t>237,744,653</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>3,795,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>3,795,000</t>
+          <t>778</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
